--- a/analise-marketing/tests/results/exportado.xlsx
+++ b/analise-marketing/tests/results/exportado.xlsx
@@ -7,8 +7,8 @@
     <sheet name="Resumo" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Disparos!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Resumo!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Disparos!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Resumo!$A$1:$P$2</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -403,93 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
-  <cols>
-    <col min="1" max="1" width="38.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="21.83203125" customWidth="1"/>
-    <col min="5" max="5" width="21.83203125" customWidth="1"/>
-    <col min="6" max="6" width="21.83203125" customWidth="1"/>
-    <col min="7" max="7" width="21.83203125" customWidth="1"/>
-    <col min="8" max="8" width="21.83203125" customWidth="1"/>
-    <col min="9" max="9" width="21.83203125" customWidth="1"/>
-    <col min="10" max="10" width="21.83203125" customWidth="1"/>
-    <col min="11" max="11" width="21.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>campanha</v>
-      </c>
-      <c r="B1" t="str">
-        <v>data de envio</v>
-      </c>
-      <c r="C1" t="str">
-        <v>enviados</v>
-      </c>
-      <c r="D1" t="str">
-        <v>entregues</v>
-      </c>
-      <c r="E1" t="str">
-        <v>visualização</v>
-      </c>
-      <c r="F1" t="str">
-        <v>lidos</v>
-      </c>
-      <c r="G1" t="str">
-        <v>cliques</v>
-      </c>
-      <c r="H1" t="str">
-        <v>taxa de abertura</v>
-      </c>
-      <c r="I1" t="str">
-        <v>taxa de cliques</v>
-      </c>
-      <c r="J1" t="str">
-        <v>canal</v>
-      </c>
-      <c r="K1" t="str">
-        <v>opt-out</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Ação; setembro</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-09-24</v>
-      </c>
-      <c r="C2">
-        <v>1000</v>
-      </c>
-      <c r="D2">
-        <v>900</v>
-      </c>
-      <c r="F2">
-        <v>450</v>
-      </c>
-      <c r="G2">
-        <v>90</v>
-      </c>
-      <c r="J2" t="str">
-        <v>E-mail</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K2"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -503,88 +417,216 @@
     <col min="10" max="10" width="21.83203125" customWidth="1"/>
     <col min="11" max="11" width="21.83203125" customWidth="1"/>
     <col min="12" max="12" width="21.83203125" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Campanha</v>
+        <v>empresas</v>
       </c>
       <c r="B1" t="str">
-        <v>Canal</v>
+        <v>colaboradores</v>
       </c>
       <c r="C1" t="str">
-        <v>Disparos</v>
+        <v>campanha</v>
       </c>
       <c r="D1" t="str">
-        <v>Enviados</v>
+        <v>data de envio</v>
       </c>
       <c r="E1" t="str">
-        <v>Entregues</v>
+        <v>enviados</v>
       </c>
       <c r="F1" t="str">
-        <v>Aberturas efetivas</v>
+        <v>entregues</v>
       </c>
       <c r="G1" t="str">
-        <v>Cliques efetivos</v>
+        <v>visualização</v>
       </c>
       <c r="H1" t="str">
-        <v>Taxa de abertura</v>
+        <v>lidos</v>
       </c>
       <c r="I1" t="str">
-        <v>CTR</v>
+        <v>cliques</v>
       </c>
       <c r="J1" t="str">
-        <v>Opt-out</v>
+        <v>taxa de abertura</v>
       </c>
       <c r="K1" t="str">
-        <v>Cobertura opt-out</v>
+        <v>taxa de cliques</v>
       </c>
       <c r="L1" t="str">
-        <v>Último envio</v>
+        <v>canal</v>
+      </c>
+      <c r="M1" t="str">
+        <v>opt-out</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Aurora</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Colaborador não informado</v>
+      </c>
+      <c r="C2" t="str">
         <v>Ação; setembro</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2">
+        <v>900</v>
+      </c>
+      <c r="H2">
+        <v>450</v>
+      </c>
+      <c r="I2">
+        <v>90</v>
+      </c>
+      <c r="L2" t="str">
         <v>E-mail</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1000</v>
-      </c>
-      <c r="E2">
-        <v>900</v>
-      </c>
-      <c r="F2">
-        <v>450</v>
-      </c>
-      <c r="G2">
-        <v>90</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="J2">
+      <c r="M2">
         <v>2</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Completo</v>
-      </c>
-      <c r="L2" t="str">
-        <v>2026-09-24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:M2"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P2"/>
+  <cols>
+    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" customWidth="1"/>
+    <col min="9" max="9" width="21.83203125" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" customWidth="1"/>
+    <col min="11" max="11" width="21.83203125" customWidth="1"/>
+    <col min="12" max="12" width="21.83203125" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" customWidth="1"/>
+    <col min="14" max="14" width="21.83203125" customWidth="1"/>
+    <col min="15" max="15" width="21.83203125" customWidth="1"/>
+    <col min="16" max="16" width="21.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Empresa</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Colaborador</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Campanha</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Canal</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Empresas atendidas</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Campanhas atendidas</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Disparos</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Enviados</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Entregues</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Aberturas efetivas</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Cliques efetivos</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Taxa de abertura</v>
+      </c>
+      <c r="M1" t="str">
+        <v>CTR</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Opt-out</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Cobertura opt-out</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Último envio</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Aurora</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Colaborador não informado</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>E-mail</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1000</v>
+      </c>
+      <c r="I2">
+        <v>900</v>
+      </c>
+      <c r="J2">
+        <v>450</v>
+      </c>
+      <c r="K2">
+        <v>90</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Completo</v>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-09-24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>